--- a/catalogs/RESOURCE_RELATIONSHIP_MAP.xlsx
+++ b/catalogs/RESOURCE_RELATIONSHIP_MAP.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue" sheetId="1" r:id="Ra7b2ab5626b44787"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESOURCE_RELATIONSHIP_MAP" sheetId="1" r:id="Rd364d831b5af45e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,41 +13,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:i/>
       <x:sz val="11"/>
-      <x:color rgb="FF25272D"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Aptos"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FF25272D"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="9"/>
-      <x:color rgb="FF25272D"/>
-      <x:name val="Carlito"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -56,170 +39,73 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF7B1734"/>
+        <x:fgColor rgb="FF6B2230"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF7F1E7"/>
+        <x:fgColor rgb="FFF5F0E7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF25272D"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC7AA74"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFDF8"/>
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="2">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="51">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ResourceRelationshipMapTable" displayName="ResourceRelationshipMapTable" ref="A5:F20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="6">
-    <x:tableColumn id="1" name="chapter"/>
-    <x:tableColumn id="2" name="chapter_title"/>
-    <x:tableColumn id="3" name="core_resources"/>
-    <x:tableColumn id="4" name="guides"/>
-    <x:tableColumn id="5" name="worked_case"/>
-    <x:tableColumn id="6" name="python_applications"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,354 +303,259 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="31" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="48" t="str">
-        <x:v>Chapter and Resource Relationship Map</x:v>
-      </x:c>
-      <x:c r="B1" s="48"/>
-      <x:c r="C1" s="48"/>
-      <x:c r="D1" s="48"/>
-      <x:c r="E1" s="48"/>
-      <x:c r="F1" s="48"/>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
+    <x:row r="1" ht="45" customHeight="1">
+      <x:c r="A1" s="9" t="str">
+        <x:v>chapter</x:v>
+      </x:c>
+      <x:c r="B1" s="9" t="str">
+        <x:v>chapter_title</x:v>
+      </x:c>
+      <x:c r="C1" s="9" t="str">
+        <x:v>core_resources</x:v>
+      </x:c>
+      <x:c r="D1" s="9" t="str">
+        <x:v>guides</x:v>
+      </x:c>
+      <x:c r="E1" s="9" t="str">
+        <x:v>worked_case</x:v>
+      </x:c>
+      <x:c r="F1" s="9" t="str">
+        <x:v>python_applications</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="45" customHeight="1">
       <x:c r="A2" s="12" t="str">
-        <x:v>A chapter-level view of core records, guides, worked examples, and Python modules.</x:v>
-      </x:c>
-      <x:c r="B2" s="12"/>
-      <x:c r="C2" s="12"/>
-      <x:c r="D2" s="12"/>
-      <x:c r="E2" s="12"/>
-      <x:c r="F2" s="12"/>
-    </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="49" t="str">
-        <x:v>Digital Resource Companion V1.0 · 2026 · stable identifiers should be used in preference to printed page numbers</x:v>
-      </x:c>
-      <x:c r="B3" s="49"/>
-      <x:c r="C3" s="49"/>
-      <x:c r="D3" s="49"/>
-      <x:c r="E3" s="49"/>
-      <x:c r="F3" s="49"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="50"/>
-      <x:c r="B4" s="50"/>
-      <x:c r="C4" s="50"/>
-      <x:c r="D4" s="50"/>
-      <x:c r="E4" s="50"/>
-      <x:c r="F4" s="50"/>
-    </x:row>
-    <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="25" t="str">
-        <x:v>chapter</x:v>
-      </x:c>
-      <x:c r="B5" s="25" t="str">
-        <x:v>chapter_title</x:v>
-      </x:c>
-      <x:c r="C5" s="25" t="str">
-        <x:v>core_resources</x:v>
-      </x:c>
-      <x:c r="D5" s="25" t="str">
-        <x:v>guides</x:v>
-      </x:c>
-      <x:c r="E5" s="25" t="str">
-        <x:v>worked_case</x:v>
-      </x:c>
-      <x:c r="F5" s="25" t="str">
-        <x:v>python_applications</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="37" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="37" t="str">
-        <x:v>AI as a Health-System Intervention</x:v>
-      </x:c>
-      <x:c r="C6" s="37" t="str">
+      <x:c r="B2" s="12" t="str">
+        <x:v>AI as a Health System Intervention</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
         <x:v>AIHE-A01; AIHE-A02</x:v>
       </x:c>
-      <x:c r="D6" s="37" t="str">
+      <x:c r="D2" s="12" t="str">
         <x:v>AIHE-RG07</x:v>
       </x:c>
-      <x:c r="E6" s="37" t="str">
+      <x:c r="E2" s="12" t="str">
         <x:v>AIHE-CASE01</x:v>
       </x:c>
-      <x:c r="F6" s="37" t="str"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="46" t="str">
+      <x:c r="F2" s="12" t="str"/>
+    </x:row>
+    <x:row r="3" ht="45" customHeight="1">
+      <x:c r="A3" s="14" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="B3" s="14" t="str">
         <x:v>Institutional Readiness and Digital Foundations</x:v>
       </x:c>
-      <x:c r="C7" s="46" t="str">
+      <x:c r="C3" s="14" t="str">
         <x:v>AIHE-A03; AIHE-A04</x:v>
       </x:c>
-      <x:c r="D7" s="46" t="str"/>
-      <x:c r="E7" s="46" t="str">
+      <x:c r="D3" s="14" t="str"/>
+      <x:c r="E3" s="14" t="str">
         <x:v>AIHE-CASE02</x:v>
       </x:c>
-      <x:c r="F7" s="46" t="str">
+      <x:c r="F3" s="14" t="str">
         <x:v>AIHE-PY01; AIHE-PY03; AIHE-PY33</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="37" t="str">
+    <x:row r="4" ht="45" customHeight="1">
+      <x:c r="A4" s="12" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="37" t="str">
+      <x:c r="B4" s="12" t="str">
         <x:v>Human–AI Decision Systems and Managerial Action</x:v>
       </x:c>
-      <x:c r="C8" s="37" t="str">
+      <x:c r="C4" s="12" t="str">
         <x:v>AIHE-C04</x:v>
       </x:c>
-      <x:c r="D8" s="37" t="str"/>
-      <x:c r="E8" s="37" t="str">
+      <x:c r="D4" s="12" t="str"/>
+      <x:c r="E4" s="12" t="str">
         <x:v>AIHE-CASE03; AIHE-CASE03B</x:v>
       </x:c>
-      <x:c r="F8" s="37" t="str">
+      <x:c r="F4" s="12" t="str">
         <x:v>AIHE-PY06; AIHE-PY21; AIHE-PY34; AIHE-PY35</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="46" t="str">
+    <x:row r="5" ht="45" customHeight="1">
+      <x:c r="A5" s="14" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="46" t="str">
+      <x:c r="B5" s="14" t="str">
         <x:v>Productivity, Work Redesign, and Implementation</x:v>
       </x:c>
-      <x:c r="C9" s="46" t="str">
+      <x:c r="C5" s="14" t="str">
         <x:v>AIHE-B03</x:v>
       </x:c>
-      <x:c r="D9" s="46" t="str">
+      <x:c r="D5" s="14" t="str">
         <x:v>AIHE-RG03</x:v>
       </x:c>
-      <x:c r="E9" s="46" t="str">
+      <x:c r="E5" s="14" t="str">
         <x:v>AIHE-CASE04</x:v>
       </x:c>
-      <x:c r="F9" s="46" t="str">
+      <x:c r="F5" s="14" t="str">
         <x:v>AIHE-PY22; AIHE-PY23; AIHE-PY28</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="37" t="str">
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="12" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="37" t="str">
+      <x:c r="B6" s="12" t="str">
         <x:v>Quality Management, Accreditation, and Organizational Learning</x:v>
       </x:c>
-      <x:c r="C10" s="37" t="str">
+      <x:c r="C6" s="12" t="str">
         <x:v>AIHE-C01; AIHE-C02</x:v>
       </x:c>
-      <x:c r="D10" s="37" t="str"/>
-      <x:c r="E10" s="37" t="str">
+      <x:c r="D6" s="12" t="str"/>
+      <x:c r="E6" s="12" t="str">
         <x:v>AIHE-CASE05</x:v>
       </x:c>
-      <x:c r="F10" s="37" t="str">
+      <x:c r="F6" s="12" t="str">
         <x:v>AIHE-PY02</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="46" t="str">
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="14" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="B7" s="14" t="str">
         <x:v>Lifecycle Cost, Pricing, and Benefit Realization</x:v>
       </x:c>
-      <x:c r="C11" s="46" t="str">
+      <x:c r="C7" s="14" t="str">
         <x:v>AIHE-B01; AIHE-B02; AIHE-B03</x:v>
       </x:c>
-      <x:c r="D11" s="46" t="str"/>
-      <x:c r="E11" s="46" t="str">
+      <x:c r="D7" s="14" t="str"/>
+      <x:c r="E7" s="14" t="str">
         <x:v>AIHE-CASE06; AIHE-CASE06B</x:v>
       </x:c>
-      <x:c r="F11" s="46" t="str">
+      <x:c r="F7" s="14" t="str">
         <x:v>AIHE-PY10; AIHE-PY11</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="37" t="str">
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="12" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="37" t="str">
+      <x:c r="B8" s="12" t="str">
         <x:v>Economic Evaluation, Affordability, and Health Technology Assessment</x:v>
       </x:c>
-      <x:c r="C12" s="37" t="str">
+      <x:c r="C8" s="12" t="str">
         <x:v>AIHE-B04</x:v>
       </x:c>
-      <x:c r="D12" s="37" t="str"/>
-      <x:c r="E12" s="37" t="str">
+      <x:c r="D8" s="12" t="str"/>
+      <x:c r="E8" s="12" t="str">
         <x:v>AIHE-CASE07</x:v>
       </x:c>
-      <x:c r="F12" s="37" t="str">
+      <x:c r="F8" s="12" t="str">
         <x:v>AIHE-PY12; AIHE-PY13; AIHE-PY16</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="46" t="str">
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="14" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="B9" s="14" t="str">
         <x:v>Decision Modelling, Simulation, and the Value of Information</x:v>
       </x:c>
-      <x:c r="C13" s="46" t="str">
+      <x:c r="C9" s="14" t="str">
         <x:v>AIHE-B05</x:v>
       </x:c>
-      <x:c r="D13" s="46" t="str">
+      <x:c r="D9" s="14" t="str">
         <x:v>AIHE-RG05</x:v>
       </x:c>
-      <x:c r="E13" s="46" t="str">
+      <x:c r="E9" s="14" t="str">
         <x:v>AIHE-CASE08; AIHE-CASE08B</x:v>
       </x:c>
-      <x:c r="F13" s="46" t="str">
+      <x:c r="F9" s="14" t="str">
         <x:v>AIHE-PY14; AIHE-PY15; AIHE-PY18; AIHE-PY19; AIHE-PY20</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="37" t="str">
+    <x:row r="10" ht="45" customHeight="1">
+      <x:c r="A10" s="12" t="str">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B14" s="37" t="str">
+      <x:c r="B10" s="12" t="str">
         <x:v>Problem-First Procurement and Vendor Governance</x:v>
       </x:c>
-      <x:c r="C14" s="37" t="str">
+      <x:c r="C10" s="12" t="str">
         <x:v>AIHE-D01</x:v>
       </x:c>
-      <x:c r="D14" s="37" t="str"/>
-      <x:c r="E14" s="37" t="str">
+      <x:c r="D10" s="12" t="str"/>
+      <x:c r="E10" s="12" t="str">
         <x:v>AIHE-CASE09; AIHE-CASE09B</x:v>
       </x:c>
-      <x:c r="F14" s="37" t="str">
+      <x:c r="F10" s="12" t="str">
         <x:v>AIHE-PY17; AIHE-PY25</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="46" t="str">
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="14" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B15" s="46" t="str">
+      <x:c r="B11" s="14" t="str">
         <x:v>Governance, Accountability, and Institutional Risk</x:v>
       </x:c>
-      <x:c r="C15" s="46" t="str">
+      <x:c r="C11" s="14" t="str">
         <x:v>AIHE-C03; AIHE-C05</x:v>
       </x:c>
-      <x:c r="D15" s="46" t="str">
+      <x:c r="D11" s="14" t="str">
         <x:v>AIHE-RG04</x:v>
       </x:c>
-      <x:c r="E15" s="46" t="str">
+      <x:c r="E11" s="14" t="str">
         <x:v>AIHE-CASE10</x:v>
       </x:c>
-      <x:c r="F15" s="46" t="str">
+      <x:c r="F11" s="14" t="str">
         <x:v>AIHE-PY07; AIHE-PY08; AIHE-PY26</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="37" t="str">
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="12" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B16" s="37" t="str">
+      <x:c r="B12" s="12" t="str">
         <x:v>Evidence, Validation, and Real-World Evaluation</x:v>
       </x:c>
-      <x:c r="C16" s="37" t="str"/>
-      <x:c r="D16" s="37" t="str">
+      <x:c r="C12" s="12" t="str"/>
+      <x:c r="D12" s="12" t="str">
         <x:v>AIHE-RG02; AIHE-RG06</x:v>
       </x:c>
-      <x:c r="E16" s="37" t="str">
+      <x:c r="E12" s="12" t="str">
         <x:v>AIHE-CASE11</x:v>
       </x:c>
-      <x:c r="F16" s="37" t="str">
+      <x:c r="F12" s="12" t="str">
         <x:v>AIHE-PY04; AIHE-PY05; AIHE-PY24; AIHE-PY30; AIHE-PY31; AIHE-PY32</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="46" t="str">
+    <x:row r="13" ht="45" customHeight="1">
+      <x:c r="A13" s="14" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="46" t="str">
+      <x:c r="B13" s="14" t="str">
         <x:v>Decision Architecture and Lifecycle Governance</x:v>
       </x:c>
-      <x:c r="C17" s="46" t="str">
+      <x:c r="C13" s="14" t="str">
         <x:v>AIHE-D02; AIHE-D03; AIHE-D04; AIHE-D05</x:v>
       </x:c>
-      <x:c r="D17" s="46" t="str">
+      <x:c r="D13" s="14" t="str">
         <x:v>AIHE-RG01</x:v>
       </x:c>
-      <x:c r="E17" s="46" t="str">
+      <x:c r="E13" s="14" t="str">
         <x:v>AIHE-CASE12</x:v>
       </x:c>
-      <x:c r="F17" s="46" t="str">
+      <x:c r="F13" s="14" t="str">
         <x:v>AIHE-PY09; AIHE-PY27; AIHE-PY29; AIHE-PY40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="37" t="str">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B18" s="37" t="str">
-        <x:v>Circular Health Systems and Resource Stewardship</x:v>
-      </x:c>
-      <x:c r="C18" s="37" t="str">
-        <x:v>AIHE-E01</x:v>
-      </x:c>
-      <x:c r="D18" s="37" t="str"/>
-      <x:c r="E18" s="37" t="str">
-        <x:v>AIHE-CASE13; AIHE-CASE13B</x:v>
-      </x:c>
-      <x:c r="F18" s="37" t="str">
-        <x:v>AIHE-PY36; AIHE-PY39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="46" t="str">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B19" s="46" t="str">
-        <x:v>Circular Procurement and Asset Stewardship</x:v>
-      </x:c>
-      <x:c r="C19" s="46" t="str">
-        <x:v>AIHE-E02; AIHE-E03</x:v>
-      </x:c>
-      <x:c r="D19" s="46" t="str"/>
-      <x:c r="E19" s="46" t="str">
-        <x:v>AIHE-CASE14</x:v>
-      </x:c>
-      <x:c r="F19" s="46" t="str">
-        <x:v>AIHE-PY37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="38" t="str">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B20" s="38" t="str">
-        <x:v>Circularity-Adjusted Economic Evaluation and Sustainable Value</x:v>
-      </x:c>
-      <x:c r="C20" s="38" t="str">
-        <x:v>AIHE-E04; AIHE-E05</x:v>
-      </x:c>
-      <x:c r="D20" s="38" t="str"/>
-      <x:c r="E20" s="38" t="str">
-        <x:v>AIHE-CASE15</x:v>
-      </x:c>
-      <x:c r="F20" s="38" t="str">
-        <x:v>AIHE-PY38; AIHE-PY39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25de65b9ac654a97"/>
-  </x:tableParts>
 </x:worksheet>
 </file>